--- a/培训日报/培训专用测试点文件夹/无畏契约冲分活动测试点/薛宇璇_无畏契约测试用例.xlsx
+++ b/培训日报/培训专用测试点文件夹/无畏契约冲分活动测试点/薛宇璇_无畏契约测试用例.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Student\Notes\Obsidian-Notes\培训日报\培训专用测试点文件夹\无畏契约冲分活动测试点\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6E64EAD3-8F88-4DDA-AF2F-755ACBE1B453}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D974A473-C3B5-4F08-825D-47D9CED500FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{3FD941B1-F213-4A82-AFDF-B691F8E46074}"/>
   </bookViews>
@@ -1485,17 +1485,12 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1537,6 +1532,18 @@
         <fgColor rgb="FFE2EFDA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor theme="0"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -1567,18 +1574,18 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1587,28 +1594,34 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1934,7 +1947,7 @@
     <col min="4" max="4" width="38.5546875" customWidth="1"/>
     <col min="5" max="5" width="54.21875" customWidth="1"/>
     <col min="6" max="6" width="48.33203125" customWidth="1"/>
-    <col min="7" max="7" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.109375" style="15" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="36.21875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1983,7 +1996,7 @@
       <c r="F3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="16" t="s">
         <v>7</v>
       </c>
       <c r="H3" s="4" t="s">
@@ -2012,10 +2025,10 @@
       <c r="F4" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="H4" s="8" t="s">
+      <c r="H4" s="7" t="s">
         <v>17</v>
       </c>
       <c r="I4" s="6" t="s">
@@ -2041,10 +2054,10 @@
       <c r="F5" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="G5" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="H5" s="10" t="s">
+      <c r="H5" s="8" t="s">
         <v>25</v>
       </c>
       <c r="I5" s="6" t="s">
@@ -2070,10 +2083,10 @@
       <c r="F6" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="G6" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="H6" s="8" t="s">
+      <c r="H6" s="7" t="s">
         <v>17</v>
       </c>
       <c r="I6" s="6"/>
@@ -2097,10 +2110,10 @@
       <c r="F7" s="6" t="s">
         <v>382</v>
       </c>
-      <c r="G7" s="7" t="s">
+      <c r="G7" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="H7" s="8" t="s">
+      <c r="H7" s="7" t="s">
         <v>17</v>
       </c>
       <c r="I7" s="6"/>
@@ -2124,10 +2137,10 @@
       <c r="F8" s="6" t="s">
         <v>382</v>
       </c>
-      <c r="G8" s="9" t="s">
+      <c r="G8" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="H8" s="8" t="s">
+      <c r="H8" s="7" t="s">
         <v>17</v>
       </c>
       <c r="I8" s="6" t="s">
@@ -2153,10 +2166,10 @@
       <c r="F9" s="6" t="s">
         <v>383</v>
       </c>
-      <c r="G9" s="9" t="s">
+      <c r="G9" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="H9" s="8" t="s">
+      <c r="H9" s="7" t="s">
         <v>17</v>
       </c>
       <c r="I9" s="6" t="s">
@@ -2182,10 +2195,10 @@
       <c r="F10" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="G10" s="9" t="s">
+      <c r="G10" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="H10" s="11" t="s">
+      <c r="H10" s="9" t="s">
         <v>52</v>
       </c>
       <c r="I10" s="6" t="s">
@@ -2211,10 +2224,10 @@
       <c r="F11" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="G11" s="9" t="s">
+      <c r="G11" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="H11" s="11" t="s">
+      <c r="H11" s="9" t="s">
         <v>52</v>
       </c>
       <c r="I11" s="6" t="s">
@@ -2240,10 +2253,10 @@
       <c r="F12" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="G12" s="9" t="s">
+      <c r="G12" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="H12" s="11" t="s">
+      <c r="H12" s="9" t="s">
         <v>52</v>
       </c>
       <c r="I12" s="6" t="s">
@@ -2269,10 +2282,10 @@
       <c r="F13" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="G13" s="7" t="s">
+      <c r="G13" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="H13" s="10" t="s">
+      <c r="H13" s="8" t="s">
         <v>25</v>
       </c>
       <c r="I13" s="6" t="s">
@@ -2298,10 +2311,10 @@
       <c r="F14" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="G14" s="9" t="s">
+      <c r="G14" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="H14" s="10" t="s">
+      <c r="H14" s="8" t="s">
         <v>25</v>
       </c>
       <c r="I14" s="6" t="s">
@@ -2327,10 +2340,10 @@
       <c r="F15" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="G15" s="9" t="s">
+      <c r="G15" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="H15" s="11" t="s">
+      <c r="H15" s="9" t="s">
         <v>52</v>
       </c>
       <c r="I15" s="6"/>
@@ -2354,10 +2367,10 @@
       <c r="F16" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="G16" s="12" t="s">
+      <c r="G16" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="H16" s="8" t="s">
+      <c r="H16" s="7" t="s">
         <v>17</v>
       </c>
       <c r="I16" s="6" t="s">
@@ -2383,10 +2396,10 @@
       <c r="F17" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="G17" s="9" t="s">
+      <c r="G17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="H17" s="11" t="s">
+      <c r="H17" s="9" t="s">
         <v>52</v>
       </c>
       <c r="I17" s="6"/>
@@ -2410,10 +2423,10 @@
       <c r="F18" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="G18" s="12" t="s">
+      <c r="G18" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="H18" s="11" t="s">
+      <c r="H18" s="9" t="s">
         <v>52</v>
       </c>
       <c r="I18" s="6" t="s">
@@ -2439,10 +2452,10 @@
       <c r="F19" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="G19" s="9" t="s">
+      <c r="G19" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="H19" s="11" t="s">
+      <c r="H19" s="9" t="s">
         <v>52</v>
       </c>
       <c r="I19" s="6" t="s">
@@ -2468,10 +2481,10 @@
       <c r="F20" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="G20" s="9" t="s">
+      <c r="G20" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="H20" s="11" t="s">
+      <c r="H20" s="9" t="s">
         <v>52</v>
       </c>
       <c r="I20" s="6" t="s">
@@ -2497,10 +2510,10 @@
       <c r="F21" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="G21" s="9" t="s">
+      <c r="G21" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="H21" s="13" t="s">
+      <c r="H21" s="10" t="s">
         <v>117</v>
       </c>
       <c r="I21" s="6" t="s">
@@ -2526,10 +2539,10 @@
       <c r="F22" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="G22" s="9" t="s">
+      <c r="G22" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="H22" s="8" t="s">
+      <c r="H22" s="7" t="s">
         <v>17</v>
       </c>
       <c r="I22" s="6"/>
@@ -2553,10 +2566,10 @@
       <c r="F23" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="G23" s="9" t="s">
+      <c r="G23" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="H23" s="8" t="s">
+      <c r="H23" s="7" t="s">
         <v>17</v>
       </c>
       <c r="I23" s="6" t="s">
@@ -2582,10 +2595,10 @@
       <c r="F24" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="G24" s="9" t="s">
+      <c r="G24" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="H24" s="8" t="s">
+      <c r="H24" s="7" t="s">
         <v>17</v>
       </c>
       <c r="I24" s="6" t="s">
@@ -2611,10 +2624,10 @@
       <c r="F25" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="G25" s="12" t="s">
+      <c r="G25" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="H25" s="8" t="s">
+      <c r="H25" s="7" t="s">
         <v>17</v>
       </c>
       <c r="I25" s="6" t="s">
@@ -2640,10 +2653,10 @@
       <c r="F26" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="G26" s="12" t="s">
+      <c r="G26" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="H26" s="11" t="s">
+      <c r="H26" s="9" t="s">
         <v>52</v>
       </c>
       <c r="I26" s="6" t="s">
@@ -2669,10 +2682,10 @@
       <c r="F27" s="6" t="s">
         <v>154</v>
       </c>
-      <c r="G27" s="9" t="s">
+      <c r="G27" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="H27" s="8" t="s">
+      <c r="H27" s="7" t="s">
         <v>17</v>
       </c>
       <c r="I27" s="6" t="s">
@@ -2698,10 +2711,10 @@
       <c r="F28" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="G28" s="12" t="s">
+      <c r="G28" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="H28" s="8" t="s">
+      <c r="H28" s="7" t="s">
         <v>17</v>
       </c>
       <c r="I28" s="6" t="s">
@@ -2727,10 +2740,10 @@
       <c r="F29" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="G29" s="12" t="s">
+      <c r="G29" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="H29" s="8" t="s">
+      <c r="H29" s="7" t="s">
         <v>17</v>
       </c>
       <c r="I29" s="6" t="s">
@@ -2756,10 +2769,10 @@
       <c r="F30" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="G30" s="12" t="s">
+      <c r="G30" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="H30" s="8" t="s">
+      <c r="H30" s="7" t="s">
         <v>17</v>
       </c>
       <c r="I30" s="6" t="s">
@@ -2785,10 +2798,10 @@
       <c r="F31" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="G31" s="9" t="s">
+      <c r="G31" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="H31" s="14" t="s">
+      <c r="H31" s="11" t="s">
         <v>179</v>
       </c>
       <c r="I31" s="6" t="s">
@@ -2814,10 +2827,10 @@
       <c r="F32" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="G32" s="9" t="s">
+      <c r="G32" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="H32" s="14" t="s">
+      <c r="H32" s="11" t="s">
         <v>179</v>
       </c>
       <c r="I32" s="6" t="s">
@@ -2843,10 +2856,10 @@
       <c r="F33" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="G33" s="9" t="s">
+      <c r="G33" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="H33" s="14" t="s">
+      <c r="H33" s="11" t="s">
         <v>179</v>
       </c>
       <c r="I33" s="6" t="s">
@@ -2872,10 +2885,10 @@
       <c r="F34" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="G34" s="12" t="s">
+      <c r="G34" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="H34" s="8" t="s">
+      <c r="H34" s="7" t="s">
         <v>17</v>
       </c>
       <c r="I34" s="6" t="s">
@@ -2901,10 +2914,10 @@
       <c r="F35" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="G35" s="12" t="s">
+      <c r="G35" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="H35" s="8" t="s">
+      <c r="H35" s="7" t="s">
         <v>17</v>
       </c>
       <c r="I35" s="6" t="s">
@@ -2930,10 +2943,10 @@
       <c r="F36" s="6" t="s">
         <v>209</v>
       </c>
-      <c r="G36" s="12" t="s">
+      <c r="G36" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="H36" s="8" t="s">
+      <c r="H36" s="7" t="s">
         <v>17</v>
       </c>
       <c r="I36" s="6" t="s">
@@ -2959,10 +2972,10 @@
       <c r="F37" s="6" t="s">
         <v>215</v>
       </c>
-      <c r="G37" s="12" t="s">
+      <c r="G37" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="H37" s="8" t="s">
+      <c r="H37" s="7" t="s">
         <v>17</v>
       </c>
       <c r="I37" s="6" t="s">
@@ -2988,10 +3001,10 @@
       <c r="F38" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="G38" s="9" t="s">
+      <c r="G38" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="H38" s="13" t="s">
+      <c r="H38" s="10" t="s">
         <v>117</v>
       </c>
       <c r="I38" s="6" t="s">
@@ -3017,10 +3030,10 @@
       <c r="F39" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="G39" s="9" t="s">
+      <c r="G39" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="H39" s="13" t="s">
+      <c r="H39" s="10" t="s">
         <v>117</v>
       </c>
       <c r="I39" s="6" t="s">
@@ -3046,10 +3059,10 @@
       <c r="F40" s="6" t="s">
         <v>232</v>
       </c>
-      <c r="G40" s="9" t="s">
+      <c r="G40" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="H40" s="13" t="s">
+      <c r="H40" s="10" t="s">
         <v>117</v>
       </c>
       <c r="I40" s="6" t="s">
@@ -3075,10 +3088,10 @@
       <c r="F41" s="6" t="s">
         <v>239</v>
       </c>
-      <c r="G41" s="9" t="s">
+      <c r="G41" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="H41" s="14" t="s">
+      <c r="H41" s="11" t="s">
         <v>179</v>
       </c>
       <c r="I41" s="6" t="s">
@@ -3104,10 +3117,10 @@
       <c r="F42" s="6" t="s">
         <v>244</v>
       </c>
-      <c r="G42" s="9" t="s">
+      <c r="G42" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="H42" s="14" t="s">
+      <c r="H42" s="11" t="s">
         <v>179</v>
       </c>
       <c r="I42" s="6" t="s">
@@ -3133,10 +3146,10 @@
       <c r="F43" s="6" t="s">
         <v>244</v>
       </c>
-      <c r="G43" s="9" t="s">
+      <c r="G43" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="H43" s="14" t="s">
+      <c r="H43" s="11" t="s">
         <v>179</v>
       </c>
       <c r="I43" s="6" t="s">
@@ -3162,10 +3175,10 @@
       <c r="F44" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="G44" s="12" t="s">
+      <c r="G44" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="H44" s="11" t="s">
+      <c r="H44" s="9" t="s">
         <v>52</v>
       </c>
       <c r="I44" s="6" t="s">
@@ -3191,10 +3204,10 @@
       <c r="F45" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="G45" s="12" t="s">
+      <c r="G45" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="H45" s="11" t="s">
+      <c r="H45" s="9" t="s">
         <v>52</v>
       </c>
       <c r="I45" s="6" t="s">
@@ -3220,10 +3233,10 @@
       <c r="F46" s="6" t="s">
         <v>266</v>
       </c>
-      <c r="G46" s="12" t="s">
+      <c r="G46" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="H46" s="11" t="s">
+      <c r="H46" s="9" t="s">
         <v>52</v>
       </c>
       <c r="I46" s="6" t="s">
@@ -3249,10 +3262,10 @@
       <c r="F47" s="6" t="s">
         <v>272</v>
       </c>
-      <c r="G47" s="12" t="s">
+      <c r="G47" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="H47" s="11" t="s">
+      <c r="H47" s="9" t="s">
         <v>52</v>
       </c>
       <c r="I47" s="6" t="s">
@@ -3278,10 +3291,10 @@
       <c r="F48" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="G48" s="12" t="s">
+      <c r="G48" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="H48" s="11" t="s">
+      <c r="H48" s="9" t="s">
         <v>52</v>
       </c>
       <c r="I48" s="6" t="s">
@@ -3307,10 +3320,10 @@
       <c r="F49" s="6" t="s">
         <v>283</v>
       </c>
-      <c r="G49" s="12" t="s">
+      <c r="G49" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="H49" s="13" t="s">
+      <c r="H49" s="10" t="s">
         <v>117</v>
       </c>
       <c r="I49" s="6" t="s">
@@ -3336,10 +3349,10 @@
       <c r="F50" s="6" t="s">
         <v>287</v>
       </c>
-      <c r="G50" s="12" t="s">
+      <c r="G50" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="H50" s="13" t="s">
+      <c r="H50" s="10" t="s">
         <v>117</v>
       </c>
       <c r="I50" s="6" t="s">
@@ -3365,10 +3378,10 @@
       <c r="F51" s="6" t="s">
         <v>292</v>
       </c>
-      <c r="G51" s="12" t="s">
+      <c r="G51" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="H51" s="11" t="s">
+      <c r="H51" s="9" t="s">
         <v>52</v>
       </c>
       <c r="I51" s="6" t="s">
@@ -3394,10 +3407,10 @@
       <c r="F52" s="6" t="s">
         <v>299</v>
       </c>
-      <c r="G52" s="12" t="s">
+      <c r="G52" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="H52" s="8" t="s">
+      <c r="H52" s="7" t="s">
         <v>17</v>
       </c>
       <c r="I52" s="6" t="s">
@@ -3423,10 +3436,10 @@
       <c r="F53" s="6" t="s">
         <v>305</v>
       </c>
-      <c r="G53" s="12" t="s">
+      <c r="G53" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="H53" s="8" t="s">
+      <c r="H53" s="7" t="s">
         <v>17</v>
       </c>
       <c r="I53" s="6" t="s">
@@ -3452,10 +3465,10 @@
       <c r="F54" s="6" t="s">
         <v>311</v>
       </c>
-      <c r="G54" s="12" t="s">
+      <c r="G54" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="H54" s="8" t="s">
+      <c r="H54" s="7" t="s">
         <v>17</v>
       </c>
       <c r="I54" s="6" t="s">
@@ -3481,10 +3494,10 @@
       <c r="F55" s="6" t="s">
         <v>317</v>
       </c>
-      <c r="G55" s="12" t="s">
+      <c r="G55" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="H55" s="11" t="s">
+      <c r="H55" s="9" t="s">
         <v>52</v>
       </c>
       <c r="I55" s="6" t="s">
@@ -3510,10 +3523,10 @@
       <c r="F56" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="G56" s="12" t="s">
+      <c r="G56" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="H56" s="8" t="s">
+      <c r="H56" s="7" t="s">
         <v>17</v>
       </c>
       <c r="I56" s="6" t="s">
@@ -3539,10 +3552,10 @@
       <c r="F57" s="6" t="s">
         <v>330</v>
       </c>
-      <c r="G57" s="12" t="s">
+      <c r="G57" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="H57" s="8" t="s">
+      <c r="H57" s="7" t="s">
         <v>17</v>
       </c>
       <c r="I57" s="6" t="s">
@@ -3568,10 +3581,10 @@
       <c r="F58" s="6" t="s">
         <v>336</v>
       </c>
-      <c r="G58" s="12" t="s">
+      <c r="G58" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="H58" s="8" t="s">
+      <c r="H58" s="7" t="s">
         <v>17</v>
       </c>
       <c r="I58" s="6" t="s">
@@ -3597,10 +3610,10 @@
       <c r="F59" s="6" t="s">
         <v>342</v>
       </c>
-      <c r="G59" s="12" t="s">
+      <c r="G59" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="H59" s="11" t="s">
+      <c r="H59" s="9" t="s">
         <v>52</v>
       </c>
       <c r="I59" s="6" t="s">
@@ -3626,10 +3639,10 @@
       <c r="F60" s="6" t="s">
         <v>348</v>
       </c>
-      <c r="G60" s="12" t="s">
+      <c r="G60" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="H60" s="8" t="s">
+      <c r="H60" s="7" t="s">
         <v>17</v>
       </c>
       <c r="I60" s="6" t="s">
@@ -3655,10 +3668,10 @@
       <c r="F61" s="6" t="s">
         <v>354</v>
       </c>
-      <c r="G61" s="12" t="s">
+      <c r="G61" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="H61" s="11" t="s">
+      <c r="H61" s="9" t="s">
         <v>52</v>
       </c>
       <c r="I61" s="6" t="s">
@@ -3684,10 +3697,10 @@
       <c r="F62" s="6" t="s">
         <v>361</v>
       </c>
-      <c r="G62" s="12" t="s">
+      <c r="G62" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="H62" s="11" t="s">
+      <c r="H62" s="9" t="s">
         <v>52</v>
       </c>
       <c r="I62" s="6" t="s">
@@ -3713,10 +3726,10 @@
       <c r="F63" s="6" t="s">
         <v>367</v>
       </c>
-      <c r="G63" s="12" t="s">
+      <c r="G63" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="H63" s="13" t="s">
+      <c r="H63" s="10" t="s">
         <v>117</v>
       </c>
       <c r="I63" s="6" t="s">
@@ -3742,10 +3755,10 @@
       <c r="F64" s="6" t="s">
         <v>373</v>
       </c>
-      <c r="G64" s="9" t="s">
+      <c r="G64" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="H64" s="8" t="s">
+      <c r="H64" s="7" t="s">
         <v>17</v>
       </c>
       <c r="I64" s="6" t="s">
@@ -3771,10 +3784,10 @@
       <c r="F65" s="6" t="s">
         <v>379</v>
       </c>
-      <c r="G65" s="12" t="s">
+      <c r="G65" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="H65" s="11" t="s">
+      <c r="H65" s="9" t="s">
         <v>52</v>
       </c>
       <c r="I65" s="6" t="s">
